--- a/internal_doc/05.测试设计/参数校验/数据基本操作-参数校验测试设计.xlsx
+++ b/internal_doc/05.测试设计/参数校验/数据基本操作-参数校验测试设计.xlsx
@@ -266,11 +266,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>格式：Json对象
-{"&lt;字段名1&gt;":"&lt;值&gt;","&lt;字段名2&gt;":"&lt;值&gt;",…}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>格式：Json对象数组
 { [
   {"&lt;字段名1&gt;":"&lt;值&gt;","&lt;字段名2&gt;":"&lt;值&gt;",…},
@@ -298,44 +293,28 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1、字段名为_id
-2、字段名为非_id
-3、值类型为int
-4、值类型为long
-5、值类型为double
-6、值类型为array
-7、值类型为bool
-8、值类型为string
-9、值类型为date，闰月的最后一天
-10、值类型为timestamp，闰月的最后一天
-11、值类型为bianry
-12、值类型为regex
-13、值类型为null
-14、值类型为OID
-15、值类型为object
-16、单个字段
-17、多个字段
-18、记录大小小于16M
-19、记录大小等于16M</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、空数组
-2、数组元素多个</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、记录大小大于16M</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>1、无效值：SDB_INSERT_RETURN
 2、空值，如insert({a:1},)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>格式：Json对象
+{"&lt;字段名1&gt;":"&lt;值&gt;","&lt;字段名2&gt;":"&lt;值&gt;",…}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、空值
+2、数组元素，多个数据记录（包含所有文档类型）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>1、字段名包含无效字符：$
-2、字段值超过long精度
+2、数值超过边界值：
+a、long类型超过边界值：-998,10000
 3、字段值超过double精度
 4、字段值为空数组
 5、字段值为date，月份不存在，如13
@@ -349,6 +328,28 @@
 13、字段值为regex，$regex值不符合正则表达式
 14、字段值为regex，$options不是i/m/x/s的其中一个，如g
 15、记录大小大于16M</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、数值取边界值：
+a、long类型，范围（-999,9999）
+b、string类型，范围（-，+）
+2、字段名为非_id
+3、值类型为int
+4、值类型为long，取值边界值：-999,9999
+5、值类型为double
+6、值类型为array
+7、值类型为bool
+8、值类型为string
+9、值类型为date，闰月的最后一天
+10、值类型为timestamp，闰月的最后一天
+11、值类型为bianry
+12、值类型为regex
+13、值类型为null
+14、值类型为OID
+15、值类型为object
+18、记录大小小于16M
+19、记录大小等于16M</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -469,12 +470,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
@@ -484,6 +479,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -863,106 +864,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="5" customFormat="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="9"/>
-      <c r="F1" s="14" t="s">
+      <c r="E1" s="14"/>
+      <c r="F1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="12" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="5" customFormat="1">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-    </row>
-    <row r="3" spans="1:9" ht="337.5">
-      <c r="A3" s="13" t="s">
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+    </row>
+    <row r="3" spans="1:9" ht="364.5">
+      <c r="A3" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" s="11"/>
+    </row>
+    <row r="4" spans="1:9" ht="108">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E4" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="H3" s="13"/>
-    </row>
-    <row r="4" spans="1:9" ht="108">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" s="13" t="s">
+      <c r="F4" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4" s="11"/>
+    </row>
+    <row r="5" spans="1:9" ht="27">
+      <c r="A5" s="10"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="H4" s="13"/>
-    </row>
-    <row r="5" spans="1:9" ht="27">
-      <c r="A5" s="12"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="13" t="s">
+      <c r="D5" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="E5" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="F5" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="G5" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="G5" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="H5" s="12"/>
+      <c r="H5" s="10"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6"/>
@@ -1515,25 +1516,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="9" t="s">
         <v>15</v>
       </c>
     </row>

--- a/internal_doc/05.测试设计/参数校验/数据基本操作-参数校验测试设计.xlsx
+++ b/internal_doc/05.测试设计/参数校验/数据基本操作-参数校验测试设计.xlsx
@@ -8,9 +8,207 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="B33" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+是否和吴艳的重复？</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G37" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+每个匹配符都要测</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D58" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+确认下是不是要</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>$gt</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>互相覆盖就好了</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B106" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+与</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>remove</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>的</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>hint</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>同</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C123" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+要覆盖所有的类型</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -121,10 +319,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>4、记录大小不能超过16M</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>3、字段值取边界值：</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -166,10 +360,6 @@
   </si>
   <si>
     <t>4、记录大小超过边界值16M</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>6、字段名可以重复</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -294,10 +484,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>remove，语法：db.cs.cl.remove([cond],[hint])</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>[cond]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -503,10 +689,6 @@
   </si>
   <si>
     <t>createIndexOffline，语法：db.cs.cl.createIndexOffline(&lt;name&gt;,&lt;indexDef&gt;,[isUnique],[enforced])</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>createIdInde，语法：db.cs.cl.createIdIndex([options])</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -690,14 +872,436 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>要在update中补充，如果有多个元素符合规则，那么只会修改第一个</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>8、匹配符$et</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>14、匹配符$or，格式{$or:[{&lt;表达式1&gt;},{&lt;表达式2&gt;},...,{&lt;表达式N&gt;}]}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>15、匹配符$type，格式{&lt;字段名&gt;:{$type:&lt;BSON type&gt;}}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>12、匹配符$and</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11.1：（补充）操作一个非数组类型的字段</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11.1、使用$all操作一个非数组类型的字段时，字段值有多个</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>15.1、&lt;BSON type&gt;取值1-5、7-11、16-18</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>15.1、字段值取边界值：1、5、7、11、16、18</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>15、格式不符合：&lt;BSON type&gt;为空，&lt;BSON type&gt;是数组类型,&lt;字段名&gt;为空</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>15.1、字段值超过边界值：0、6、12、15、19</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>16、匹配符$exists，格式{&lt;字段名&gt;:{$exists:&lt;0|1&gt;}}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>17、匹配符$elemMatch，格式{&lt;字段名&gt;:{$elemMatch:{子字段名:&lt;值&gt;,...}}}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>18、匹配符$+标识符，格式{"字段名.$+标识符":value}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>18.1、只作用于数组对象</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>18.2、标识符是一个整数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>19、匹配符$size：{"&lt;字段名&gt;":{$size:"&lt;值&gt;"}}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>19.1、字段值为整数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>16、字段值取0、1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>16、格式不符合：字段值为空，字段值是字符串、字段值取2、取-1、字段名为空</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>18.1、字段名对应的是非数组对象</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>18.2、标示符不是整数：浮点数、英文字母</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>18.3、格式不符合，同$gt 3.2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>19.1、字段值超过长整型边界值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>19.2、字段值不是整数：数组类型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20、匹配符$regex，格式：{"&lt;字段名&gt;":{$regex:&lt;值&gt;,$options:&lt;值&gt;}}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>19.1、值取长整型边界值和整型边界值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>21、$mod，格式：{&lt;字段名&gt;：{$mod:[value1,value2]},...}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>21.2、value1如果是浮点型，那只会截取整数部分</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>21.1、value1是除0以外的整型数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>21.5、value2如果是浮点型，也只截取整数部分</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>21.4、value2是整型数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>21.6、value2非整型数以0处理</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>21.3、value1不能为非整型数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>21.1、value1取非0整型数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>21.1、value1取0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>21.2、value1取0.5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>21.2、value1取浮点型数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>21.6、取非整形数，如数组类型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>21.6、value2取空值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>21.4、value2取整型数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>21.5、value2取浮点型数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>21.3、value1取字符串，取空值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>22、$isnull，格式：{&lt;字段名&gt;:{$isnull: &lt;0|1&gt;}}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>22、字段值取0、1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>22、字段值取：-1、2、对象、空值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>21.7、字段值对应的对象不是整型数：数组、字符串</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[sel]</t>
+  </si>
+  <si>
+    <t>1、Json对象：{"字段名1":"值1","字段名2":"值2",...}</t>
+  </si>
+  <si>
+    <t>2、为空时，返回记录的所有字段</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3、如果记录中存在所选字段，设定的值（值1，值2...）不生效；</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、为空</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4、如果记录中不存在所选字段，则按指定的值输出，值1、值2…可为空</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、不符合Json对象，如字段名为空</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3、记录中存在所选字段</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4、记录中不存在所选字段，且值1为空，如{a:""}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>……</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>同find</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>同find()的[cond]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cursor.close()</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cursor.current()</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cursor.next()</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、括号中加参数，如数字</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>explain，语法：query.explain([option])</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[option]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、字段名为Run</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3、字段值取值true|false</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、字段名不是Run，如Runn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3、字段值取值不是布尔型，如OID型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、Json对象，默认为{Run:false}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、为空</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>i</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、取边界值：0、长整型的最大值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、取值无效：i不是整型数，如字符串</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hint(&lt;hint&gt;)，语法：query.hint(&lt;hint&gt;)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>query[i]，语法：var query = db.cs.cl.find(); query[0];</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;hint&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、字段名会被忽略</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3、为空时，表示不使用索引</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4、当字段值为 null 时，则遍历集合中所有的记录</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、不符合Json对象，如取字符串类型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3、为空</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、Json对象：{"":null} 或者 {"":"&lt;indexname&gt;"}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、字段名不为空，如{"a":&lt;indexname&gt;}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4、字段值取null</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5、&lt;indexname&gt;索引不存在时，使用表扫描</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5、索引不存在</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>limit，格式query.limit(&lt;num&gt;)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;num&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>size，格式：query.size()</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>skip，格式query.skip(&lt;num&gt;)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、取值无效：i不是整型数，如null</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sort，格式query.sort(&lt;sort&gt;)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;sort&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、字段值取1或者-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、Json对象，{&lt;字段名1&gt;:&lt;-1|1&gt;,&lt;字段名2&gt;:&lt;-1|1&gt;,...}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3、为空：相当于对返回的结果集不排序。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、字段值取值1、-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、字段值取0、2、-2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、格式不合法：字段名不存在、字段名为空、字段值为空</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>toArray，格式：query.toArray()</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>还没考虑切分表的情况</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4、记录大小不能超过16M</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6、字段名可以重复</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>c、浮点数，范围（1.7E-308 至 1.7E+308）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>findAndRemove，格式：find().remove()</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>createIdIndex，语法：db.cs.cl.createIdIndex([options])</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>remove，语法：db.cs.cl.remove([cond],[hint])</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>13、匹配符$not，格式{$not:[{&lt;表达式1&gt;},{&lt;表达式2&gt;},...,{&lt;表达式N&gt;}]}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>9、匹配符$in，格式：{&lt;字段名&gt;:{$in:[&lt;值1&gt;,&lt;值2&gt;,...&lt;值N&gt;]}}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -710,310 +1314,20 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>13、匹配符$not，格式{$not:[{&lt;表达式1&gt;},{&lt;表达式2&gt;},...,{&lt;表达式N&gt;}]}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>14、匹配符$or，格式{$or:[{&lt;表达式1&gt;},{&lt;表达式2&gt;},...,{&lt;表达式N&gt;}]}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>15、匹配符$type，格式{&lt;字段名&gt;:{$type:&lt;BSON type&gt;}}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>11.1、使用$all操作一个非数组类型的字段时，字段值只能有一个</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>12、匹配符$and</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>11.1：（补充）操作一个非数组类型的字段</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>11.1、使用$all操作一个非数组类型的字段时，字段值有多个</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>15.1、&lt;BSON type&gt;取值1-5、7-11、16-18</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>15.1、字段值取边界值：1、5、7、11、16、18</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>15、格式不符合：&lt;BSON type&gt;为空，&lt;BSON type&gt;是数组类型,&lt;字段名&gt;为空</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>15.1、字段值超过边界值：0、6、12、15、19</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>16、匹配符$exists，格式{&lt;字段名&gt;:{$exists:&lt;0|1&gt;}}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>17、匹配符$elemMatch，格式{&lt;字段名&gt;:{$elemMatch:{子字段名:&lt;值&gt;,...}}}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>18、匹配符$+标识符，格式{"字段名.$+标识符":value}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>18.1、只作用于数组对象</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>18.2、标识符是一个整数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>19、匹配符$size：{"&lt;字段名&gt;":{$size:"&lt;值&gt;"}}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>19.1、字段值为整数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>16、字段值取0、1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>16、格式不符合：字段值为空，字段值是字符串、字段值取2、取-1、字段名为空</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>18.1、字段名对应的是非数组对象</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>18.2、标示符不是整数：浮点数、英文字母</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>18.3、格式不符合，同$gt 3.2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>19.1、字段值超过长整型边界值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>19.2、字段值不是整数：数组类型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>20、匹配符$regex，格式：{"&lt;字段名&gt;":{$regex:&lt;值&gt;,$options:&lt;值&gt;}}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>19.1、值取长整型边界值和整型边界值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>21、$mod，格式：{&lt;字段名&gt;：{$mod:[value1,value2]},...}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>21.2、value1如果是浮点型，那只会截取整数部分</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>21.1、value1是除0以外的整型数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>21.5、value2如果是浮点型，也只截取整数部分</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>21.4、value2是整型数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>21.6、value2非整型数以0处理</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>21.3、value1不能为非整型数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>21.1、value1取非0整型数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>21.1、value1取0</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>21.2、value1取0.5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>21.2、value1取浮点型数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>21.6、取非整形数，如数组类型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>21.6、value2取空值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>21.4、value2取整型数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>21.5、value2取浮点型数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>21.3、value1取字符串，取空值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>22、$isnull，格式：{&lt;字段名&gt;:{$isnull: &lt;0|1&gt;}}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>22、字段值取0、1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>22、字段值取：-1、2、对象、空值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>21.7、字段值对应的对象不是整型数：数组、字符串</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[sel]</t>
-  </si>
-  <si>
-    <t>1、Json对象：{"字段名1":"值1","字段名2":"值2",...}</t>
-  </si>
-  <si>
-    <t>2、为空时，返回记录的所有字段</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3、如果记录中存在所选字段，设定的值（值1，值2...）不生效；</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2、为空</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>4、如果记录中不存在所选字段，则按指定的值输出，值1、值2…可为空</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、不符合Json对象，如字段名为空</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3、记录中存在所选字段</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>4、记录中不存在所选字段，且值1为空，如{a:""}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>findOne，语法：db.cs.cl.findOne([cond],[sel])</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>……</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>count，语法：db.cs.cl.count([cond])</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>同find</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>同find()的[cond]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cursor.close()</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cursor.current()</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cursor.next()</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、括号中加参数，如数字</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>explain，语法：query.explain([option])</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[option]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2、字段名为Run</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3、字段值取值true|false</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2、字段名不是Run，如Runn</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3、字段值取值不是布尔型，如OID型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、Json对象，默认为{Run:false}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、为空</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>count，语法：db.cs.cl.find().count([cond])</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>同db.cs.cl.count()</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>i</t>
+    <t>count，语法：db.cs.cl.count([cond]),db.cs.cl.find().count([cond])</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>1、大于等于0的长整型</t>
+      <t>1、大于等于0的整型</t>
     </r>
     <r>
       <rPr>
@@ -1024,169 +1338,56 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>？是</t>
+      <t/>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dropIndex，格式：dropIndex(&lt;name&gt;)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;name&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、格式：字符串类型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、索引名必须在集合中存在。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4、长度不超过127B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、索引名在集合中不存在</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3、索引名是空串、含点、含美元符号</t>
+  </si>
+  <si>
+    <r>
+      <t>1、数值型</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
-        <family val="2"/>
+        <family val="3"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>int还是long</t>
+      <t>？？？不做限制</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、取边界值：0、长整型的最大值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、取值无效：i不是整型数，如字符串</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>hint(&lt;hint&gt;)，语法：query.hint(&lt;hint&gt;)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>query[i]，语法：var query = db.cs.cl.find(); query[0];</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;hint&gt;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2、字段名会被忽略</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3、为空时，表示不使用索引</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>4、当字段值为 null 时，则遍历集合中所有的记录</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、不符合Json对象，如取字符串类型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3、为空</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、Json对象：{"":null} 或者 {"":"&lt;indexname&gt;"}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2、字段名不为空，如{"a":&lt;indexname&gt;}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>4、字段值取null</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>5、&lt;indexname&gt;索引不存在时，使用表扫描</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>5、索引不存在</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>limit，格式query.limit(&lt;num&gt;)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;num&gt;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>size，格式：query.size()</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>findAndRemove，格式：query.remove()</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>skip，格式query.skip(&lt;num&gt;)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、取值无效：i不是整型数，如null</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>sort，格式query.sort(&lt;sort&gt;)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;sort&gt;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2、字段值取1或者-1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、Json对象，{&lt;字段名1&gt;:&lt;-1|1&gt;,&lt;字段名2&gt;:&lt;-1|1&gt;,...}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3、为空：相当于对返回的结果集不排序。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2、字段值取值1、-1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2、字段值取0、2、-2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、格式不合法：字段名不存在、字段名为空、字段值为空</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>toArray，格式：query.toArray()</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>findAndUpdate，格式query.update(&lt;update&gt;,[returnNew])</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;update&gt;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[returnNew]</t>
-  </si>
-  <si>
-    <t>1、布尔型，默认为false</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2、格式不合法：如取时间戳</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、取true、false、空</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>同update的[rule]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>还没考虑切分表的情况</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1194,7 +1395,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1232,11 +1433,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1366,7 +1581,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1374,21 +1589,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
@@ -1399,7 +1602,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1762,11 +1976,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I153"/>
+  <dimension ref="A1:I151"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="6.125" style="10" customWidth="1"/>
-    <col min="2" max="2" width="9.625" style="7" customWidth="1"/>
+    <col min="1" max="1" width="6.125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="9.625" style="4" customWidth="1"/>
     <col min="3" max="3" width="8.875" customWidth="1"/>
     <col min="4" max="4" width="37.75" customWidth="1"/>
     <col min="5" max="5" width="4.75" customWidth="1"/>
@@ -1775,61 +1989,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="3" t="s">
+      <c r="E1" s="18"/>
+      <c r="F1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="16" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="25.5">
-      <c r="A2" s="9"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="5"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="18"/>
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="18" t="s">
-        <v>278</v>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="14" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F3" t="s">
         <v>15</v>
@@ -1840,62 +2054,62 @@
         <v>14</v>
       </c>
       <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
         <v>28</v>
-      </c>
-      <c r="G4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="D5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" t="s">
         <v>24</v>
-      </c>
-      <c r="G5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="D6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="D7" t="s">
-        <v>23</v>
+        <v>256</v>
       </c>
       <c r="F7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" t="s">
         <v>39</v>
-      </c>
-      <c r="G7" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="D8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s">
+        <v>258</v>
+      </c>
+      <c r="G8" t="s">
         <v>40</v>
-      </c>
-      <c r="G8" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="D9" t="s">
-        <v>35</v>
+        <v>257</v>
       </c>
       <c r="F9" t="s">
         <v>19</v>
       </c>
       <c r="G9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1913,7 +2127,7 @@
         <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1921,23 +2135,23 @@
         <v>18</v>
       </c>
       <c r="G13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="F14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G14" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="F15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1947,7 +2161,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="F17" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1957,280 +2171,280 @@
     </row>
     <row r="19" spans="1:7">
       <c r="F19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="F20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" s="3" customFormat="1">
+      <c r="A21" s="6"/>
+      <c r="B21" s="5"/>
+      <c r="F21" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G20" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" s="6" customFormat="1">
-      <c r="A21" s="10"/>
-      <c r="B21" s="8"/>
-      <c r="F21" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="11"/>
+      <c r="A22" s="7"/>
       <c r="C22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" t="s">
         <v>51</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>53</v>
       </c>
-      <c r="E22" t="s">
-        <v>55</v>
-      </c>
       <c r="F22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" s="6" customFormat="1">
-      <c r="B23" s="8"/>
-      <c r="F23" s="6" t="s">
         <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="3" customFormat="1">
+      <c r="B23" s="5"/>
+      <c r="F23" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="C24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" t="s">
         <v>56</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
+        <v>55</v>
+      </c>
+      <c r="F24" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E24" t="s">
-        <v>57</v>
-      </c>
-      <c r="F24" s="13" t="s">
+      <c r="G24" s="9" t="s">
         <v>60</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="D25" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F25" s="13" t="s">
+    </row>
+    <row r="26" spans="1:7" s="7" customFormat="1">
+      <c r="B26" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" s="11" customFormat="1">
-      <c r="B26" s="16" t="s">
+      <c r="D26" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F26" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="G26" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="D27" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F27" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D26" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="F26" s="11" t="s">
+    </row>
+    <row r="28" spans="1:7" s="7" customFormat="1">
+      <c r="B28" s="10"/>
+      <c r="C28" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="G26" s="11" t="s">
+      <c r="D28" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="D29" s="9" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="D27" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" s="11" customFormat="1">
-      <c r="B28" s="14"/>
-      <c r="C28" s="11" t="s">
+      <c r="F29" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G29" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="D30" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="F30" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="D31" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="F28" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="G28" s="17" t="s">
+    </row>
+    <row r="32" spans="1:7" s="7" customFormat="1">
+      <c r="B32" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="D29" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G29" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="D30" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F30" s="13" t="s">
+      <c r="D32" s="7" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="D31" s="13" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" s="11" customFormat="1">
-      <c r="B32" s="14" t="s">
+      <c r="F32" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="G32" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D32" s="11" t="s">
+    </row>
+    <row r="33" spans="1:7" s="7" customFormat="1">
+      <c r="B33" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="C33" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="G32" s="11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" s="11" customFormat="1">
-      <c r="B33" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="E33" s="11" t="s">
+    </row>
+    <row r="34" spans="1:7">
+      <c r="D34" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="D35" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" s="7" customFormat="1">
+      <c r="A36" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E36" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G33" s="11" t="s">
+      <c r="F36" s="13"/>
+      <c r="G36" s="7" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="D37" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="F37" s="9" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="D34" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="F34" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="G34" s="10" t="s">
+      <c r="G37" s="9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="F38" s="9" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="D35" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="G35" s="13" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" s="11" customFormat="1">
-      <c r="A36" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="17"/>
-      <c r="G36" s="11" t="s">
+      <c r="G38" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="D39" s="9"/>
+      <c r="G39" t="s">
         <v>147</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="D37" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="F37" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="G37" s="13" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="F38" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="G38" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="D39" s="13"/>
-      <c r="G39" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="G40" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="D41" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="F41" s="13" t="s">
-        <v>140</v>
+      <c r="D41" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>136</v>
       </c>
       <c r="G41" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="F42" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="F43" t="s">
+        <v>37</v>
+      </c>
+      <c r="G43" t="s">
         <v>39</v>
-      </c>
-      <c r="G43" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="F44" t="s">
+        <v>38</v>
+      </c>
+      <c r="G44" t="s">
         <v>40</v>
-      </c>
-      <c r="G44" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2238,7 +2452,7 @@
         <v>19</v>
       </c>
       <c r="G45" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2256,7 +2470,7 @@
         <v>17</v>
       </c>
       <c r="G48" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49" spans="4:7">
@@ -2264,23 +2478,23 @@
         <v>18</v>
       </c>
       <c r="G49" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="50" spans="4:7">
       <c r="F50" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G50" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51" spans="4:7">
       <c r="F51" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G51" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="4:7">
@@ -2290,7 +2504,7 @@
     </row>
     <row r="53" spans="4:7">
       <c r="F53" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="54" spans="4:7">
@@ -2300,1054 +2514,1050 @@
     </row>
     <row r="55" spans="4:7">
       <c r="G55" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="56" spans="4:7">
       <c r="G56" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="57" spans="4:7">
       <c r="G57" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="58" spans="4:7">
-      <c r="D58" s="13" t="s">
-        <v>142</v>
+      <c r="D58" s="9" t="s">
+        <v>138</v>
       </c>
       <c r="F58" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G58" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="59" spans="4:7">
       <c r="D59" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F59" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G59" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="60" spans="4:7">
       <c r="D60" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F60" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G60" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="61" spans="4:7">
       <c r="D61" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F61" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G61" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="62" spans="4:7">
       <c r="D62" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="F62" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G62" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="63" spans="4:7">
       <c r="D63" t="s">
-        <v>161</v>
+        <v>263</v>
       </c>
       <c r="F63" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G63" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="64" spans="4:7">
       <c r="D64" t="s">
-        <v>162</v>
+        <v>264</v>
       </c>
       <c r="F64" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G64" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="D65" t="s">
-        <v>163</v>
+        <v>265</v>
       </c>
       <c r="F65" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="D66" t="s">
-        <v>167</v>
+        <v>266</v>
       </c>
       <c r="F66" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="G66" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
     </row>
     <row r="67" spans="3:7">
       <c r="D67" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="D68" t="s">
-        <v>164</v>
-      </c>
-      <c r="F68" s="18" t="s">
-        <v>158</v>
+        <v>262</v>
+      </c>
+      <c r="F68" s="14" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="D69" t="s">
-        <v>165</v>
-      </c>
-      <c r="F69" s="18" t="s">
-        <v>158</v>
+        <v>156</v>
+      </c>
+      <c r="F69" s="14" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="D70" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="G70" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="D71" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="F71" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="G71" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="D72" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="F72" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="G72" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="D73" t="s">
-        <v>176</v>
-      </c>
-      <c r="F73" s="18" t="s">
-        <v>158</v>
+        <v>166</v>
+      </c>
+      <c r="F73" s="14" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="74" spans="3:7">
-      <c r="C74" s="18" t="s">
-        <v>159</v>
-      </c>
+      <c r="C74" s="14"/>
       <c r="D74" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="D75" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="G75" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="D76" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="G76" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="G77" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="D78" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="D79" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="F79" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="G79" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="G80" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
     </row>
     <row r="81" spans="2:7">
       <c r="D81" t="s">
-        <v>189</v>
-      </c>
-      <c r="F81" s="18" t="s">
-        <v>158</v>
+        <v>179</v>
+      </c>
+      <c r="F81" s="14" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="82" spans="2:7">
       <c r="D82" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
     </row>
     <row r="83" spans="2:7">
       <c r="D83" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="F83" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="G83" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
     </row>
     <row r="84" spans="2:7">
       <c r="D84" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="F84" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G84" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="85" spans="2:7">
       <c r="D85" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="G85" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
     </row>
     <row r="86" spans="2:7">
       <c r="D86" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="F86" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
     </row>
     <row r="87" spans="2:7">
       <c r="D87" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="F87" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="88" spans="2:7">
       <c r="D88" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="F88" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="G88" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
     </row>
     <row r="89" spans="2:7">
       <c r="G89" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
     </row>
     <row r="90" spans="2:7">
       <c r="D90" t="s">
+        <v>197</v>
+      </c>
+      <c r="F90" t="s">
+        <v>198</v>
+      </c>
+      <c r="G90" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="91" spans="2:7" s="7" customFormat="1">
+      <c r="B91" s="10"/>
+      <c r="C91" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="G91" s="7" t="s">
         <v>207</v>
-      </c>
-      <c r="F90" t="s">
-        <v>208</v>
-      </c>
-      <c r="G90" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="91" spans="2:7" s="11" customFormat="1">
-      <c r="B91" s="14"/>
-      <c r="C91" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="D91" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="G91" s="11" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="92" spans="2:7">
       <c r="D92" t="s">
-        <v>213</v>
-      </c>
-      <c r="F92" s="13" t="s">
-        <v>215</v>
+        <v>203</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="93" spans="2:7">
       <c r="D93" t="s">
-        <v>214</v>
-      </c>
-      <c r="F93" s="13" t="s">
-        <v>218</v>
+        <v>204</v>
+      </c>
+      <c r="F93" s="9" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="94" spans="2:7">
       <c r="D94" t="s">
+        <v>206</v>
+      </c>
+      <c r="F94" s="9" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="95" spans="2:7" s="7" customFormat="1">
+      <c r="B95" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="96" spans="2:7">
+      <c r="D96" s="9" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7" s="7" customFormat="1">
+      <c r="B97" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7" s="6" customFormat="1">
+      <c r="B98" s="5"/>
+      <c r="D98" s="9" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7" s="7" customFormat="1">
+      <c r="B99" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G99" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="F94" s="13" t="s">
+    </row>
+    <row r="100" spans="2:7" s="7" customFormat="1">
+      <c r="B100" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G100" s="7" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="101" spans="2:7" s="7" customFormat="1">
+      <c r="B101" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G101" s="7" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="102" spans="2:7" s="7" customFormat="1">
+      <c r="B102" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="G102" s="7" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7">
+      <c r="D103" s="9" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="95" spans="2:7" s="11" customFormat="1">
-      <c r="B95" s="14" t="s">
+      <c r="G103" s="9" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7">
+      <c r="D104" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="D95" s="11" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="96" spans="2:7">
-      <c r="D96" s="13" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="97" spans="2:7" s="11" customFormat="1">
-      <c r="B97" s="14" t="s">
+      <c r="G104" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="C97" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D97" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="E97" s="11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="98" spans="2:7" s="10" customFormat="1">
-      <c r="B98" s="8"/>
-      <c r="D98" s="13" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="99" spans="2:7" s="11" customFormat="1">
-      <c r="B99" s="14" t="s">
+    </row>
+    <row r="105" spans="2:7" s="7" customFormat="1">
+      <c r="B105" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="C105" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="C99" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D99" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="F99" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="G99" s="11" t="s">
+      <c r="D105" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="G105" s="7" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7" s="7" customFormat="1">
+      <c r="B106" s="10" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="100" spans="2:7" s="11" customFormat="1">
-      <c r="B100" s="14" t="s">
+      <c r="C106" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="G106" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7">
+      <c r="D107" t="s">
+        <v>231</v>
+      </c>
+      <c r="F107" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7">
+      <c r="D108" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="F108" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="109" spans="2:7">
+      <c r="D109" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="F109" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="110" spans="2:7">
+      <c r="D110" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="F110" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="111" spans="2:7" s="7" customFormat="1">
+      <c r="B111" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="E111" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F111" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="C100" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D100" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="F100" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="G100" s="11" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="101" spans="2:7" s="11" customFormat="1">
-      <c r="B101" s="14" t="s">
+      <c r="G111" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="C101" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D101" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="F101" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="G101" s="11" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="102" spans="2:7" s="11" customFormat="1">
-      <c r="B102" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="C102" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="D102" s="11" t="s">
+    </row>
+    <row r="112" spans="2:7" s="7" customFormat="1">
+      <c r="B112" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G112" s="7" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" s="8" customFormat="1">
+      <c r="B113" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D113" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="G113" s="8" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" s="7" customFormat="1">
+      <c r="B114" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="E114" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F114" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="G114" s="7" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" s="7" customFormat="1">
+      <c r="B115" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="E115" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G115" s="7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="D116" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="F116" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="G116" s="9" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="D117" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="F117" t="s">
         <v>235</v>
       </c>
-      <c r="E102" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="F102" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="G102" s="11" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="103" spans="2:7">
-      <c r="D103" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="G103" s="13" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="104" spans="2:7">
-      <c r="D104" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="G104" s="13" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="105" spans="2:7" s="11" customFormat="1">
-      <c r="B105" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="D105" s="11" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="106" spans="2:7">
-      <c r="D106" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="107" spans="2:7" s="11" customFormat="1">
-      <c r="B107" s="14" t="s">
-        <v>244</v>
-      </c>
-      <c r="C107" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="D107" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="E107" s="11" t="s">
+    </row>
+    <row r="118" spans="1:7" s="7" customFormat="1">
+      <c r="B118" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G118" s="7" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" s="7" customFormat="1">
+      <c r="A119" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B119" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D119" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E119" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F107" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="G107" s="11" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="108" spans="2:7" s="11" customFormat="1">
-      <c r="B108" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="C108" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="D108" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="G108" s="11" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="109" spans="2:7">
-      <c r="D109" t="s">
-        <v>246</v>
-      </c>
-      <c r="F109" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="110" spans="2:7">
-      <c r="D110" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="F110" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="111" spans="2:7">
-      <c r="D111" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="F111" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="112" spans="2:7">
-      <c r="D112" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="F112" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" s="11" customFormat="1">
-      <c r="B113" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="C113" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="D113" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="E113" s="11" t="s">
+      <c r="F119" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G119" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" s="6" customFormat="1">
+      <c r="B120" s="4"/>
+      <c r="D120" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="G120" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" s="6" customFormat="1">
+      <c r="B121" s="4"/>
+      <c r="D121" t="s">
+        <v>96</v>
+      </c>
+      <c r="G121" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="D122" t="s">
+        <v>97</v>
+      </c>
+      <c r="F122" t="s">
+        <v>98</v>
+      </c>
+      <c r="G122" s="9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" s="7" customFormat="1">
+      <c r="B123" s="10"/>
+      <c r="C123" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D123" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E123" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F113" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="G113" s="11" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" s="11" customFormat="1">
-      <c r="B114" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="C114" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D114" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="F114" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="G114" s="11" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" s="12" customFormat="1">
-      <c r="B115" s="19" t="s">
-        <v>258</v>
-      </c>
-      <c r="C115" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D115" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="F115" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="G115" s="12" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" s="11" customFormat="1">
-      <c r="B116" s="14" t="s">
+    </row>
+    <row r="124" spans="1:7">
+      <c r="D124" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F124" t="s">
+        <v>88</v>
+      </c>
+      <c r="G124" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="D125" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F125" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="G125" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="G126" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" s="7" customFormat="1">
+      <c r="B127" s="10"/>
+      <c r="C127" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E127" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G127" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="D128" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="G128" s="9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" s="7" customFormat="1">
+      <c r="B129" s="10"/>
+      <c r="C129" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F129" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G129" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="D130" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="F130" s="9"/>
+      <c r="G130" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="D131" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="G131" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" s="7" customFormat="1">
+      <c r="B132" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E132" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F132" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G132" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="C133" s="6"/>
+      <c r="D133" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E133" s="6"/>
+      <c r="F133" s="6"/>
+      <c r="G133" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="C134" s="6"/>
+      <c r="D134" t="s">
+        <v>96</v>
+      </c>
+      <c r="E134" s="6"/>
+      <c r="F134" s="6"/>
+      <c r="G134" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="D135" t="s">
+        <v>275</v>
+      </c>
+      <c r="F135" t="s">
+        <v>98</v>
+      </c>
+      <c r="G135" s="9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="A136" s="7"/>
+      <c r="B136" s="10"/>
+      <c r="C136" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D136" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E136" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F136" s="7"/>
+      <c r="G136" s="7"/>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="D137" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F137" t="s">
+        <v>88</v>
+      </c>
+      <c r="G137" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="D138" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F138" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="G138" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="G139" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140" s="7"/>
+      <c r="B140" s="10"/>
+      <c r="C140" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E140" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F140" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G140" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="D141" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="G141" s="9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142" s="7"/>
+      <c r="B142" s="10"/>
+      <c r="C142" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E142" s="7"/>
+      <c r="F142" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G142" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="D143" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="F143" s="9"/>
+      <c r="G143" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="D144" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="G144" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="145" spans="2:7" s="7" customFormat="1">
+      <c r="B145" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="C116" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="D116" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="E116" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F116" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="G116" s="11" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" s="11" customFormat="1">
-      <c r="B117" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="C117" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="D117" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="E117" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G117" s="11" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7">
-      <c r="D118" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="F118" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="G118" s="13" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7">
-      <c r="D119" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="F119" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" s="11" customFormat="1">
-      <c r="B120" s="14" t="s">
+      <c r="C145" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F145" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G145" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="146" spans="2:7">
+      <c r="D146" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G146" s="9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="147" spans="2:7" s="7" customFormat="1">
+      <c r="B147" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F147" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G147" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="148" spans="2:7" s="7" customFormat="1">
+      <c r="B148" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="C120" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D120" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="F120" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="G120" s="11" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" s="11" customFormat="1">
-      <c r="B121" s="14" t="s">
+      <c r="C148" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="C121" s="11" t="s">
+      <c r="D148" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="D121" s="20" t="s">
+      <c r="E148" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="F148" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G148" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="149" spans="2:7">
+      <c r="D149" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="G149" s="6" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="150" spans="2:7">
+      <c r="D150" t="s">
+        <v>96</v>
+      </c>
+      <c r="G150" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
-      <c r="D122" s="13" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7">
-      <c r="C123" t="s">
-        <v>273</v>
-      </c>
-      <c r="D123" t="s">
-        <v>274</v>
-      </c>
-      <c r="E123" t="s">
-        <v>57</v>
-      </c>
-      <c r="F123" t="s">
-        <v>276</v>
-      </c>
-      <c r="G123" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" s="11" customFormat="1">
-      <c r="A124" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="B124" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C124" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="D124" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="E124" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F124" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="G124" s="11" t="s">
+    <row r="151" spans="2:7">
+      <c r="D151" t="s">
+        <v>97</v>
+      </c>
+      <c r="F151" t="s">
+        <v>98</v>
+      </c>
+      <c r="G151" s="9" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" s="10" customFormat="1">
-      <c r="B125" s="7"/>
-      <c r="D125" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="G125" s="10" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" s="10" customFormat="1">
-      <c r="B126" s="7"/>
-      <c r="D126" t="s">
-        <v>99</v>
-      </c>
-      <c r="G126" s="10" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7">
-      <c r="D127" t="s">
-        <v>100</v>
-      </c>
-      <c r="F127" t="s">
-        <v>101</v>
-      </c>
-      <c r="G127" s="13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" s="11" customFormat="1">
-      <c r="B128" s="14"/>
-      <c r="C128" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D128" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E128" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7">
-      <c r="D129" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="F129" t="s">
-        <v>91</v>
-      </c>
-      <c r="G129" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7">
-      <c r="D130" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="F130" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="G130" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7">
-      <c r="G131" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" s="11" customFormat="1">
-      <c r="B132" s="14"/>
-      <c r="C132" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D132" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="E132" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="F132" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="G132" s="11" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7">
-      <c r="D133" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="G133" s="13" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" s="11" customFormat="1">
-      <c r="B134" s="14"/>
-      <c r="C134" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D134" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="F134" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="G134" s="11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7">
-      <c r="D135" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="F135" s="13"/>
-      <c r="G135" s="13" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7">
-      <c r="D136" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="G136" s="13" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" s="11" customFormat="1">
-      <c r="B137" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="C137" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="D137" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="E137" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F137" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="G137" s="11" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7">
-      <c r="C138" s="10"/>
-      <c r="D138" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="E138" s="10"/>
-      <c r="F138" s="10"/>
-      <c r="G138" s="10" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7">
-      <c r="C139" s="10"/>
-      <c r="D139" t="s">
-        <v>99</v>
-      </c>
-      <c r="E139" s="10"/>
-      <c r="F139" s="10"/>
-      <c r="G139" s="10" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7">
-      <c r="D140" t="s">
-        <v>100</v>
-      </c>
-      <c r="F140" t="s">
-        <v>101</v>
-      </c>
-      <c r="G140" s="13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7">
-      <c r="A141" s="11"/>
-      <c r="B141" s="14"/>
-      <c r="C141" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D141" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E141" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F141" s="11"/>
-      <c r="G141" s="11"/>
-    </row>
-    <row r="142" spans="1:7">
-      <c r="D142" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="F142" t="s">
-        <v>91</v>
-      </c>
-      <c r="G142" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7">
-      <c r="D143" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="F143" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="G143" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7">
-      <c r="G144" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7">
-      <c r="A145" s="11"/>
-      <c r="B145" s="14"/>
-      <c r="C145" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D145" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="E145" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="F145" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="G145" s="11" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7">
-      <c r="D146" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="G146" s="13" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7">
-      <c r="A147" s="11"/>
-      <c r="B147" s="14"/>
-      <c r="C147" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D147" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="E147" s="11"/>
-      <c r="F147" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="G147" s="11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7">
-      <c r="D148" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="F148" s="13"/>
-      <c r="G148" s="13" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7">
-      <c r="D149" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="G149" s="13" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" s="11" customFormat="1">
-      <c r="B150" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C150" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="D150" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="F150" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="G150" s="11" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7">
-      <c r="D151" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="G151" s="13" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" s="11" customFormat="1">
-      <c r="B152" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="C152" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D152" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="F152" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="G152" s="11" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" s="11" customFormat="1">
-      <c r="B153" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -3361,5 +3571,17 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>